--- a/jogos_2025-04-29.xlsx
+++ b/jogos_2025-04-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="188">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -229,24 +175,24 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Norway Toppserien</t>
+  </si>
+  <si>
     <t>Austria 2. Liga</t>
   </si>
   <si>
-    <t>Norway Toppserien</t>
+    <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
@@ -274,18 +220,33 @@
     <t>Tokyo</t>
   </si>
   <si>
+    <t>Blaublitz Akita</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
+  </si>
+  <si>
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
     <t>Yokohama</t>
   </si>
   <si>
-    <t>Iwaki</t>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
+    <t>Kataller Toyama</t>
   </si>
   <si>
     <t>Oita Trinita</t>
   </si>
   <si>
+    <t>Consadole Sapporo</t>
+  </si>
+  <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
     <t>Nagoya Grampus</t>
   </si>
   <si>
@@ -295,33 +256,18 @@
     <t>Ventforet Kofu</t>
   </si>
   <si>
-    <t>Consadole Sapporo</t>
-  </si>
-  <si>
-    <t>Kataller Toyama</t>
-  </si>
-  <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
-    <t>Blaublitz Akita</t>
-  </si>
-  <si>
-    <t>Fagiano Okayama</t>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
+    <t>Jubilo Iwata</t>
   </si>
   <si>
     <t>Gamba Osaka</t>
   </si>
   <si>
-    <t>Jubilo Iwata</t>
-  </si>
-  <si>
-    <t>Cerezo Osaka</t>
-  </si>
-  <si>
-    <t>Shonan Bellmare</t>
-  </si>
-  <si>
     <t>Ehime</t>
   </si>
   <si>
@@ -331,39 +277,39 @@
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Trondheims-Ørn</t>
+  </si>
+  <si>
+    <t>Hønefoss Women</t>
+  </si>
+  <si>
+    <t>Stabæk Women</t>
+  </si>
+  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Sturm Graz II</t>
   </si>
   <si>
-    <t>Stabæk Women</t>
+    <t>Brann W</t>
   </si>
   <si>
     <t>Lyn W</t>
   </si>
   <si>
-    <t>Trondheims-Ørn</t>
-  </si>
-  <si>
-    <t>Hønefoss Women</t>
-  </si>
-  <si>
-    <t>Brann W</t>
+    <t>Falkenberg</t>
   </si>
   <si>
     <t>Malmö FF</t>
   </si>
   <si>
+    <t>ENPPI</t>
+  </si>
+  <si>
     <t>Hødd</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
-  </si>
-  <si>
     <t>Almería</t>
   </si>
   <si>
@@ -379,27 +325,42 @@
     <t>Casa Pia</t>
   </si>
   <si>
+    <t>Platense</t>
+  </si>
+  <si>
     <t>Newell's Old Boys</t>
   </si>
   <si>
-    <t>Platense</t>
-  </si>
-  <si>
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
+    <t>Tokushima Vortis</t>
+  </si>
+  <si>
+    <t>Omiya Ardija</t>
+  </si>
+  <si>
     <t>Albirex Niigata</t>
   </si>
   <si>
     <t>Kashima Antlers</t>
   </si>
   <si>
-    <t>Omiya Ardija</t>
+    <t>Tokyo Verdy</t>
+  </si>
+  <si>
+    <t>Montedio Yamagata</t>
   </si>
   <si>
     <t>Sagan Tosu</t>
   </si>
   <si>
+    <t>V-Varen Nagasaki</t>
+  </si>
+  <si>
+    <t>JEF United</t>
+  </si>
+  <si>
     <t>Kashiwa Reysol</t>
   </si>
   <si>
@@ -409,33 +370,18 @@
     <t>Vegalta Sendai</t>
   </si>
   <si>
-    <t>V-Varen Nagasaki</t>
-  </si>
-  <si>
-    <t>Montedio Yamagata</t>
-  </si>
-  <si>
-    <t>JEF United</t>
-  </si>
-  <si>
-    <t>Tokushima Vortis</t>
-  </si>
-  <si>
-    <t>Tokyo Verdy</t>
+    <t>Machida Zelvia</t>
+  </si>
+  <si>
+    <t>Avispa Fukuoka</t>
+  </si>
+  <si>
+    <t>Renofa Yamaguchi</t>
   </si>
   <si>
     <t>Kyoto Sanga</t>
   </si>
   <si>
-    <t>Renofa Yamaguchi</t>
-  </si>
-  <si>
-    <t>Machida Zelvia</t>
-  </si>
-  <si>
-    <t>Avispa Fukuoka</t>
-  </si>
-  <si>
     <t>Fujieda MYFC</t>
   </si>
   <si>
@@ -445,39 +391,39 @@
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
+    <t>Kolbotn</t>
+  </si>
+  <si>
+    <t>Vålerenga Women</t>
+  </si>
+  <si>
+    <t>Røa Women</t>
+  </si>
+  <si>
     <t>Gareji</t>
   </si>
   <si>
     <t>First Vienna</t>
   </si>
   <si>
-    <t>Røa Women</t>
+    <t>Lillestrøm W</t>
   </si>
   <si>
     <t>Bodø / Glimt W</t>
   </si>
   <si>
-    <t>Kolbotn</t>
-  </si>
-  <si>
-    <t>Vålerenga Women</t>
-  </si>
-  <si>
-    <t>Lillestrøm W</t>
+    <t>Örebro</t>
   </si>
   <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>Ghazl El Mehalla</t>
+  </si>
+  <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Ghazl El Mehalla</t>
-  </si>
-  <si>
     <t>Racing Club de Ferrol</t>
   </si>
   <si>
@@ -493,12 +439,12 @@
     <t>GD Estoril Praia</t>
   </si>
   <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
     <t>Huracán</t>
   </si>
   <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
     <t>complete</t>
   </si>
   <si>
@@ -511,45 +457,45 @@
     <t>['13']</t>
   </si>
   <si>
+    <t>['76', '90+3']</t>
+  </si>
+  <si>
     <t>['2']</t>
   </si>
   <si>
     <t>['58']</t>
   </si>
   <si>
-    <t>['76', '90+3']</t>
+    <t>['90+6']</t>
   </si>
   <si>
     <t>['10', '27']</t>
   </si>
   <si>
-    <t>['90+6']</t>
-  </si>
-  <si>
     <t>['53', '67']</t>
   </si>
   <si>
     <t>['-1']</t>
   </si>
   <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['8', '41']</t>
+  </si>
+  <si>
     <t>['12', '33', '40', '63']</t>
   </si>
   <si>
-    <t>['8', '41']</t>
-  </si>
-  <si>
-    <t>['90+3']</t>
-  </si>
-  <si>
     <t>['11']</t>
   </si>
   <si>
+    <t>['2', '54']</t>
+  </si>
+  <si>
     <t>['32', '46']</t>
   </si>
   <si>
-    <t>['2', '54']</t>
-  </si>
-  <si>
     <t>['55']</t>
   </si>
   <si>
@@ -562,22 +508,31 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['51', '53']</t>
+  </si>
+  <si>
     <t>['43', '81']</t>
   </si>
   <si>
-    <t>['51', '53']</t>
-  </si>
-  <si>
     <t>['45+1', '79']</t>
   </si>
   <si>
+    <t>['32', '36']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
     <t>['85']</t>
   </si>
   <si>
     <t>['49', '67', '77']</t>
   </si>
   <si>
-    <t>['90+5']</t>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['38', '51']</t>
   </si>
   <si>
     <t>['33', '50']</t>
@@ -586,37 +541,28 @@
     <t>['29', '55']</t>
   </si>
   <si>
-    <t>['38', '51']</t>
-  </si>
-  <si>
-    <t>['32', '36']</t>
-  </si>
-  <si>
-    <t>['66']</t>
+    <t>['49', '78']</t>
   </si>
   <si>
     <t>['33']</t>
   </si>
   <si>
-    <t>['49', '78']</t>
-  </si>
-  <si>
     <t>['5', '12', '14', '19']</t>
   </si>
   <si>
+    <t>['25', '61', '76', '83']</t>
+  </si>
+  <si>
     <t>['73']</t>
   </si>
   <si>
-    <t>['25', '61', '76', '83']</t>
-  </si>
-  <si>
     <t>['67']</t>
   </si>
   <si>
+    <t>['5']</t>
+  </si>
+  <si>
     <t>['40']</t>
-  </si>
-  <si>
-    <t>['5']</t>
   </si>
   <si>
     <t>['90+2']</t>
@@ -995,10 +941,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD39"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,79 +1059,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45776</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1200,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L2">
         <v>2.87</v>
@@ -1275,156 +1167,102 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK2" t="s">
-        <v>184</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>5</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.2</v>
-      </c>
-      <c r="BC2">
-        <v>1.83</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>166</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45776.04513888889</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45776</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>2.89</v>
       </c>
       <c r="M3">
-        <v>3.78</v>
+        <v>3.32</v>
       </c>
       <c r="N3">
-        <v>5.6</v>
+        <v>2.36</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U3">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1433,10 +1271,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1445,93 +1283,39 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK3" t="s">
-        <v>185</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>7</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.44</v>
-      </c>
-      <c r="BC3">
-        <v>3.25</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45776</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1540,43 +1324,43 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L4">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="M4">
-        <v>3.03</v>
+        <v>3.66</v>
       </c>
       <c r="N4">
-        <v>2.61</v>
+        <v>2.07</v>
       </c>
       <c r="O4">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1585,28 +1369,28 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AD4">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1615,90 +1399,36 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AK4" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>8</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.2</v>
-      </c>
-      <c r="BC4">
-        <v>1.91</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>168</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45776</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1710,37 +1440,37 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L5">
-        <v>3.2</v>
+        <v>1.59</v>
       </c>
       <c r="M5">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="N5">
-        <v>2.07</v>
+        <v>5.6</v>
       </c>
       <c r="O5">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="R5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T5">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1749,10 +1479,10 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1761,22 +1491,22 @@
         <v>0</v>
       </c>
       <c r="AB5">
+        <v>1.95</v>
+      </c>
+      <c r="AC5">
         <v>1.7</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>2.05</v>
       </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1.83</v>
-      </c>
       <c r="AG5">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1785,126 +1515,72 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="AK5" t="s">
-        <v>187</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>8</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.4</v>
-      </c>
-      <c r="BC5">
-        <v>1.73</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>169</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45776</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L6">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="M6">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="N6">
-        <v>2.92</v>
+        <v>2.61</v>
       </c>
       <c r="O6">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S6">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T6">
         <v>3.5</v>
@@ -1931,22 +1607,22 @@
         <v>2.4</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AC6">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG6">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1955,120 +1631,66 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AK6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>14</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.05</v>
-      </c>
-      <c r="BC6">
-        <v>2.05</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>170</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45776</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L7">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="M7">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N7">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="O7">
+        <v>1.91</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>2.25</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>1.95</v>
       </c>
       <c r="R7">
         <v>1.57</v>
@@ -2101,16 +1723,16 @@
         <v>2.37</v>
       </c>
       <c r="AB7">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AD7">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <v>2.1</v>
@@ -2125,87 +1747,33 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="AK7" t="s">
-        <v>188</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>10</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.25</v>
-      </c>
-      <c r="BC7">
-        <v>1.95</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>171</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45776</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2220,50 +1788,50 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L8">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="M8">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="N8">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="O8">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U8">
+        <v>1.36</v>
+      </c>
+      <c r="V8">
+        <v>8</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>3.42</v>
+      </c>
+      <c r="Y8">
         <v>1.33</v>
       </c>
-      <c r="V8">
-        <v>9</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>2.68</v>
-      </c>
-      <c r="Y8">
-        <v>1.48</v>
-      </c>
       <c r="Z8">
         <v>0</v>
       </c>
@@ -2271,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -2283,10 +1851,10 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -2295,138 +1863,84 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>10</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>2.2</v>
-      </c>
-      <c r="BC8">
-        <v>1.83</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45776</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L9">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="M9">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N9">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="O9">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R9">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -2441,22 +1955,22 @@
         <v>2.4</v>
       </c>
       <c r="AB9">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AD9">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -2465,87 +1979,33 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>7</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.25</v>
-      </c>
-      <c r="BC9">
-        <v>1.83</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45776</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2560,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L10">
         <v>2.86</v>
@@ -2635,87 +2095,33 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="AK10" t="s">
-        <v>190</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>8</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>2.1</v>
-      </c>
-      <c r="BC10">
-        <v>1.73</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>172</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45776</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2730,74 +2136,74 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L11">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="M11">
-        <v>3.51</v>
+        <v>3.86</v>
       </c>
       <c r="N11">
-        <v>2.52</v>
+        <v>1.93</v>
       </c>
       <c r="O11">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
+        <v>1.67</v>
+      </c>
+      <c r="R11">
+        <v>1.33</v>
+      </c>
+      <c r="S11">
+        <v>3.25</v>
+      </c>
+      <c r="T11">
+        <v>2.63</v>
+      </c>
+      <c r="U11">
+        <v>1.44</v>
+      </c>
+      <c r="V11">
+        <v>6.5</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>3.22</v>
+      </c>
+      <c r="Y11">
+        <v>1.36</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>1.53</v>
+      </c>
+      <c r="AC11">
+        <v>2.25</v>
+      </c>
+      <c r="AD11">
+        <v>2.33</v>
+      </c>
+      <c r="AE11">
+        <v>1.53</v>
+      </c>
+      <c r="AF11">
+        <v>1.67</v>
+      </c>
+      <c r="AG11">
         <v>2.1</v>
       </c>
-      <c r="R11">
-        <v>1.4</v>
-      </c>
-      <c r="S11">
-        <v>2.75</v>
-      </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
-      <c r="U11">
-        <v>1.36</v>
-      </c>
-      <c r="V11">
-        <v>8</v>
-      </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>3.42</v>
-      </c>
-      <c r="Y11">
-        <v>1.33</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>1.77</v>
-      </c>
-      <c r="AC11">
-        <v>1.98</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>1.73</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
       <c r="AH11">
         <v>0</v>
       </c>
@@ -2805,169 +2211,115 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>9</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.83</v>
-      </c>
-      <c r="BC11">
-        <v>2.1</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45776</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L12">
-        <v>3.41</v>
+        <v>2.86</v>
       </c>
       <c r="M12">
-        <v>3.86</v>
+        <v>2.9</v>
       </c>
       <c r="N12">
-        <v>1.93</v>
+        <v>2.66</v>
       </c>
       <c r="O12">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
+        <v>1.95</v>
+      </c>
+      <c r="R12">
+        <v>1.57</v>
+      </c>
+      <c r="S12">
+        <v>2.25</v>
+      </c>
+      <c r="T12">
+        <v>3.75</v>
+      </c>
+      <c r="U12">
+        <v>1.25</v>
+      </c>
+      <c r="V12">
+        <v>11</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>1.48</v>
+      </c>
+      <c r="AA12">
+        <v>2.37</v>
+      </c>
+      <c r="AB12">
+        <v>2.67</v>
+      </c>
+      <c r="AC12">
+        <v>1.44</v>
+      </c>
+      <c r="AD12">
+        <v>2.83</v>
+      </c>
+      <c r="AE12">
+        <v>1.46</v>
+      </c>
+      <c r="AF12">
+        <v>2.1</v>
+      </c>
+      <c r="AG12">
         <v>1.67</v>
       </c>
-      <c r="R12">
-        <v>1.33</v>
-      </c>
-      <c r="S12">
-        <v>3.25</v>
-      </c>
-      <c r="T12">
-        <v>2.63</v>
-      </c>
-      <c r="U12">
-        <v>1.44</v>
-      </c>
-      <c r="V12">
-        <v>6.5</v>
-      </c>
-      <c r="W12">
-        <v>1.11</v>
-      </c>
-      <c r="X12">
-        <v>3.22</v>
-      </c>
-      <c r="Y12">
-        <v>1.36</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>1.53</v>
-      </c>
-      <c r="AC12">
-        <v>2.25</v>
-      </c>
-      <c r="AD12">
-        <v>2.33</v>
-      </c>
-      <c r="AE12">
-        <v>1.53</v>
-      </c>
-      <c r="AF12">
-        <v>1.67</v>
-      </c>
-      <c r="AG12">
-        <v>2.1</v>
-      </c>
       <c r="AH12">
         <v>0</v>
       </c>
@@ -2975,156 +2327,102 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="AK12" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>11</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2.38</v>
-      </c>
-      <c r="BC12">
-        <v>1.67</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>173</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45776</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L13">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="M13">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N13">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="R13">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S13">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T13">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -3133,10 +2431,10 @@
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -3145,168 +2443,114 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>10</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>2.25</v>
-      </c>
-      <c r="BC13">
-        <v>1.95</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45776</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>1</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L14">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="M14">
-        <v>2.85</v>
+        <v>3.41</v>
       </c>
       <c r="N14">
+        <v>2.67</v>
+      </c>
+      <c r="O14">
+        <v>2.25</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>1.83</v>
+      </c>
+      <c r="R14">
+        <v>1.5</v>
+      </c>
+      <c r="S14">
+        <v>2.5</v>
+      </c>
+      <c r="T14">
+        <v>3.4</v>
+      </c>
+      <c r="U14">
+        <v>1.3</v>
+      </c>
+      <c r="V14">
+        <v>10</v>
+      </c>
+      <c r="W14">
+        <v>1.06</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>1.5</v>
+      </c>
+      <c r="AA14">
+        <v>2.4</v>
+      </c>
+      <c r="AB14">
+        <v>1.87</v>
+      </c>
+      <c r="AC14">
+        <v>1.87</v>
+      </c>
+      <c r="AD14">
         <v>2.95</v>
       </c>
-      <c r="O14">
+      <c r="AE14">
+        <v>1.41</v>
+      </c>
+      <c r="AF14">
         <v>1.91</v>
       </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>2.25</v>
-      </c>
-      <c r="R14">
-        <v>1.57</v>
-      </c>
-      <c r="S14">
-        <v>2.25</v>
-      </c>
-      <c r="T14">
-        <v>3.75</v>
-      </c>
-      <c r="U14">
-        <v>1.25</v>
-      </c>
-      <c r="V14">
-        <v>11</v>
-      </c>
-      <c r="W14">
-        <v>1.05</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>1.48</v>
-      </c>
-      <c r="AA14">
-        <v>2.37</v>
-      </c>
-      <c r="AB14">
-        <v>2.6</v>
-      </c>
-      <c r="AC14">
-        <v>1.46</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>2.1</v>
-      </c>
       <c r="AG14">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -3315,120 +2559,66 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="AK14" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>10</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.91</v>
-      </c>
-      <c r="BC14">
-        <v>2.25</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>174</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45776.08333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45776</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
         <v>2</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
       <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>143</v>
+      </c>
+      <c r="L15">
+        <v>2.63</v>
+      </c>
+      <c r="M15">
+        <v>3.23</v>
+      </c>
+      <c r="N15">
+        <v>2.63</v>
+      </c>
+      <c r="O15">
         <v>2</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="s">
-        <v>161</v>
-      </c>
-      <c r="L15">
-        <v>2.3</v>
-      </c>
-      <c r="M15">
-        <v>3.2</v>
-      </c>
-      <c r="N15">
-        <v>3.1</v>
-      </c>
-      <c r="O15">
-        <v>1.73</v>
-      </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="R15">
         <v>1.44</v>
@@ -3461,16 +2651,16 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF15">
         <v>1.91</v>
@@ -3485,93 +2675,39 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>11</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.73</v>
-      </c>
-      <c r="BC15">
-        <v>2.38</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>175</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45776.125</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45776</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3580,61 +2716,61 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L16">
-        <v>1.83</v>
+        <v>2.77</v>
       </c>
       <c r="M16">
-        <v>3.79</v>
+        <v>3.06</v>
       </c>
       <c r="N16">
-        <v>3.87</v>
+        <v>2.62</v>
       </c>
       <c r="O16">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16">
+        <v>1.95</v>
+      </c>
+      <c r="R16">
+        <v>1.53</v>
+      </c>
+      <c r="S16">
+        <v>2.38</v>
+      </c>
+      <c r="T16">
+        <v>3.75</v>
+      </c>
+      <c r="U16">
+        <v>1.25</v>
+      </c>
+      <c r="V16">
+        <v>11</v>
+      </c>
+      <c r="W16">
+        <v>1.05</v>
+      </c>
+      <c r="X16">
+        <v>3.51</v>
+      </c>
+      <c r="Y16">
+        <v>1.33</v>
+      </c>
+      <c r="Z16">
+        <v>1.57</v>
+      </c>
+      <c r="AA16">
         <v>2.4</v>
       </c>
-      <c r="R16">
-        <v>1.4</v>
-      </c>
-      <c r="S16">
-        <v>2.75</v>
-      </c>
-      <c r="T16">
-        <v>3</v>
-      </c>
-      <c r="U16">
-        <v>1.36</v>
-      </c>
-      <c r="V16">
-        <v>8</v>
-      </c>
-      <c r="W16">
-        <v>1.08</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>3.29</v>
-      </c>
-      <c r="AA16">
-        <v>1.34</v>
-      </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC16">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -3643,10 +2779,10 @@
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -3655,157 +2791,103 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK16" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>12</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.67</v>
-      </c>
-      <c r="BC16">
-        <v>2.4</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45776.125</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45776</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>1</v>
       </c>
-      <c r="H17">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>143</v>
+      </c>
+      <c r="L17">
+        <v>1.83</v>
+      </c>
+      <c r="M17">
+        <v>3.79</v>
+      </c>
+      <c r="N17">
+        <v>3.87</v>
+      </c>
+      <c r="O17">
+        <v>1.67</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>2.4</v>
+      </c>
+      <c r="R17">
+        <v>1.4</v>
+      </c>
+      <c r="S17">
+        <v>2.75</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>1.36</v>
+      </c>
+      <c r="V17">
+        <v>8</v>
+      </c>
+      <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>3.29</v>
+      </c>
+      <c r="AA17">
+        <v>1.34</v>
+      </c>
+      <c r="AB17">
+        <v>1.75</v>
+      </c>
+      <c r="AC17">
         <v>2</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" t="s">
-        <v>161</v>
-      </c>
-      <c r="L17">
-        <v>2.63</v>
-      </c>
-      <c r="M17">
-        <v>3.23</v>
-      </c>
-      <c r="N17">
-        <v>2.63</v>
-      </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>2</v>
-      </c>
-      <c r="R17">
-        <v>1.44</v>
-      </c>
-      <c r="S17">
-        <v>2.63</v>
-      </c>
-      <c r="T17">
-        <v>3.25</v>
-      </c>
-      <c r="U17">
-        <v>1.33</v>
-      </c>
-      <c r="V17">
-        <v>9</v>
-      </c>
-      <c r="W17">
-        <v>1.07</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>2.1</v>
-      </c>
-      <c r="AC17">
-        <v>1.6</v>
-      </c>
       <c r="AD17">
         <v>0</v>
       </c>
@@ -3813,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -3825,168 +2907,114 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="AK17" t="s">
-        <v>194</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>2</v>
-      </c>
-      <c r="BC17">
-        <v>2</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>171</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45776.125</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45776</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
         <v>83</v>
       </c>
-      <c r="E18" t="s">
-        <v>101</v>
-      </c>
       <c r="F18" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L18">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="M18">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N18">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="R18">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S18">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V18">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AC18">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -3995,87 +3023,33 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="AK18" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18">
-        <v>5</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>2.2</v>
-      </c>
-      <c r="BC18">
-        <v>1.95</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>176</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45776.125</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45776</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -4090,7 +3064,7 @@
         <v>4</v>
       </c>
       <c r="K19" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L19">
         <v>2.6</v>
@@ -4165,87 +3139,33 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="AK19" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>2.2</v>
-      </c>
-      <c r="BC19">
-        <v>1.83</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>177</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45776.125</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45776</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -4260,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L20">
         <v>2.05</v>
@@ -4335,87 +3255,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ20" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="AK20" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL20">
-        <v>1.19</v>
-      </c>
-      <c r="AM20">
-        <v>1.28</v>
-      </c>
-      <c r="AN20">
-        <v>2</v>
-      </c>
-      <c r="AO20">
-        <v>4</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.5</v>
-      </c>
-      <c r="BC20">
-        <v>3.1</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45776.41666666666</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45776</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4430,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L21">
         <v>2.45</v>
@@ -4505,93 +3371,39 @@
         <v>1.01</v>
       </c>
       <c r="AJ21" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK21" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL21">
-        <v>1.51</v>
-      </c>
-      <c r="AM21">
-        <v>1.33</v>
-      </c>
-      <c r="AN21">
-        <v>1.4</v>
-      </c>
-      <c r="AO21">
-        <v>8</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>2.25</v>
-      </c>
-      <c r="BC21">
-        <v>1.83</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45776.5</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45776</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4600,332 +3412,224 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L22">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="M22">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="N22">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="P22">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R22">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>2.15</v>
+      </c>
+      <c r="Y22">
+        <v>1.57</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>1.4</v>
+      </c>
+      <c r="AC22">
         <v>2.75</v>
       </c>
-      <c r="T22">
-        <v>2.8</v>
-      </c>
-      <c r="U22">
-        <v>1.38</v>
-      </c>
-      <c r="V22">
-        <v>7</v>
-      </c>
-      <c r="W22">
-        <v>1.08</v>
-      </c>
-      <c r="X22">
-        <v>1.05</v>
-      </c>
-      <c r="Y22">
-        <v>9</v>
-      </c>
-      <c r="Z22">
-        <v>1.25</v>
-      </c>
-      <c r="AA22">
-        <v>3.28</v>
-      </c>
-      <c r="AB22">
-        <v>1.85</v>
-      </c>
-      <c r="AC22">
-        <v>1.8</v>
-      </c>
       <c r="AD22">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AE22">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="AK22" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL22">
-        <v>1.15</v>
-      </c>
-      <c r="AM22">
-        <v>1.24</v>
-      </c>
-      <c r="AN22">
-        <v>2.25</v>
-      </c>
-      <c r="AO22">
-        <v>10</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.36</v>
-      </c>
-      <c r="BC22">
-        <v>3.75</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45776</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23">
+        <v>6.8</v>
+      </c>
+      <c r="M23">
+        <v>4.8</v>
+      </c>
+      <c r="N23">
+        <v>1.4</v>
+      </c>
+      <c r="O23">
+        <v>3.75</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>1.29</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>1.5</v>
+      </c>
+      <c r="AC23">
+        <v>2.35</v>
+      </c>
+      <c r="AD23">
+        <v>2.25</v>
+      </c>
+      <c r="AE23">
+        <v>1.53</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>2.65</v>
+      </c>
+      <c r="AI23">
+        <v>1.4</v>
+      </c>
+      <c r="AJ23" t="s">
         <v>144</v>
       </c>
-      <c r="G23">
-        <v>4</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>3</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" t="s">
-        <v>161</v>
-      </c>
-      <c r="L23">
-        <v>3.75</v>
-      </c>
-      <c r="M23">
-        <v>3.94</v>
-      </c>
-      <c r="N23">
-        <v>1.81</v>
-      </c>
-      <c r="O23">
-        <v>2.2</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>1.67</v>
-      </c>
-      <c r="R23">
-        <v>1.24</v>
-      </c>
-      <c r="S23">
-        <v>3.5</v>
-      </c>
-      <c r="T23">
-        <v>2.25</v>
-      </c>
-      <c r="U23">
-        <v>1.57</v>
-      </c>
-      <c r="V23">
-        <v>5</v>
-      </c>
-      <c r="W23">
-        <v>1.14</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>15</v>
-      </c>
-      <c r="Z23">
-        <v>1.18</v>
-      </c>
-      <c r="AA23">
-        <v>4.5</v>
-      </c>
-      <c r="AB23">
-        <v>1.57</v>
-      </c>
-      <c r="AC23">
-        <v>2.25</v>
-      </c>
-      <c r="AD23">
-        <v>2.38</v>
-      </c>
-      <c r="AE23">
-        <v>1.58</v>
-      </c>
-      <c r="AF23">
-        <v>1.5</v>
-      </c>
-      <c r="AG23">
-        <v>2.3</v>
-      </c>
-      <c r="AH23">
-        <v>4</v>
-      </c>
-      <c r="AI23">
-        <v>1.23</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>172</v>
-      </c>
       <c r="AK23" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL23">
-        <v>1.2</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>1.24</v>
-      </c>
-      <c r="AO23">
-        <v>7</v>
-      </c>
-      <c r="AP23">
-        <v>1.18</v>
-      </c>
-      <c r="AQ23">
-        <v>1.35</v>
-      </c>
-      <c r="AR23">
-        <v>1.6</v>
-      </c>
-      <c r="AS23">
-        <v>1.96</v>
-      </c>
-      <c r="AT23">
-        <v>2.48</v>
-      </c>
-      <c r="AU23">
-        <v>4.1</v>
-      </c>
-      <c r="AV23">
-        <v>2.92</v>
-      </c>
-      <c r="AW23">
-        <v>2.19</v>
-      </c>
-      <c r="AX23">
-        <v>1.75</v>
-      </c>
-      <c r="AY23">
-        <v>1.47</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>2.2</v>
-      </c>
-      <c r="BC23">
-        <v>1.67</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>178</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45776</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -4940,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L24">
         <v>1.54</v>
@@ -5015,93 +3719,39 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="AK24" t="s">
-        <v>181</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>12</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.36</v>
-      </c>
-      <c r="BC24">
-        <v>3.5</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>163</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45776</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5110,366 +3760,258 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L25">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M25">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="N25">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="O25">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="Q25">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>3.7</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB25">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
         <v>1.8</v>
       </c>
       <c r="AD25">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AE25">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AK25" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>11</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>1.29</v>
-      </c>
-      <c r="BC25">
-        <v>4</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>153</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45776</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F26" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
         <v>1</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
       <c r="I26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L26">
-        <v>1.2</v>
+        <v>3.75</v>
       </c>
       <c r="M26">
-        <v>5.5</v>
+        <v>3.94</v>
       </c>
       <c r="N26">
-        <v>10</v>
+        <v>1.81</v>
       </c>
       <c r="O26">
+        <v>2.2</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>1.67</v>
+      </c>
+      <c r="R26">
+        <v>1.24</v>
+      </c>
+      <c r="S26">
+        <v>3.5</v>
+      </c>
+      <c r="T26">
+        <v>2.25</v>
+      </c>
+      <c r="U26">
+        <v>1.57</v>
+      </c>
+      <c r="V26">
+        <v>5</v>
+      </c>
+      <c r="W26">
+        <v>1.14</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>15</v>
+      </c>
+      <c r="Z26">
         <v>1.18</v>
       </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
+      <c r="AA26">
         <v>4.5</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>2.15</v>
-      </c>
-      <c r="Y26">
+      <c r="AB26">
         <v>1.57</v>
       </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>1.4</v>
-      </c>
       <c r="AC26">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD26">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE26">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ26" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK26" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AO26">
-        <v>11</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>1.18</v>
-      </c>
-      <c r="BC26">
-        <v>4.5</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>179</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45776</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L27">
+        <v>1.28</v>
+      </c>
+      <c r="M27">
+        <v>5.4</v>
+      </c>
+      <c r="N27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O27">
+        <v>1.22</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <v>4</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27" t="s">
-        <v>161</v>
-      </c>
-      <c r="L27">
-        <v>6.8</v>
-      </c>
-      <c r="M27">
-        <v>4.8</v>
-      </c>
-      <c r="N27">
-        <v>1.4</v>
-      </c>
-      <c r="O27">
-        <v>3.75</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>1.29</v>
-      </c>
       <c r="R27">
         <v>0</v>
       </c>
@@ -5501,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC27">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD27">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AE27">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -5519,120 +4061,66 @@
         <v>0</v>
       </c>
       <c r="AH27">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AK27" t="s">
-        <v>197</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>0</v>
-      </c>
-      <c r="AO27">
-        <v>10</v>
-      </c>
-      <c r="AP27">
-        <v>0</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27">
-        <v>0</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
-      </c>
-      <c r="AW27">
-        <v>0</v>
-      </c>
-      <c r="AX27">
-        <v>0</v>
-      </c>
-      <c r="AY27">
-        <v>0</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>3.75</v>
-      </c>
-      <c r="BC27">
-        <v>1.29</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>180</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45776</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L28">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="M28">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="N28">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="O28">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5659,10 +4147,10 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -5671,16 +4159,16 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD28">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AE28">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AF28">
         <v>0</v>
@@ -5695,767 +4183,497 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="AK28" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AO28">
-        <v>10</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.22</v>
-      </c>
-      <c r="BC28">
-        <v>4</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45776.54166666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45776</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L29">
+        <v>2.03</v>
+      </c>
+      <c r="M29">
+        <v>3.3</v>
+      </c>
+      <c r="N29">
+        <v>3.65</v>
+      </c>
+      <c r="O29">
+        <v>1.62</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>2.5</v>
+      </c>
+      <c r="R29">
         <v>1.36</v>
       </c>
-      <c r="M29">
-        <v>5.2</v>
-      </c>
-      <c r="N29">
-        <v>7</v>
-      </c>
-      <c r="O29">
-        <v>1.2</v>
-      </c>
-      <c r="P29">
-        <v>15</v>
-      </c>
-      <c r="Q29">
-        <v>5</v>
-      </c>
-      <c r="R29">
-        <v>1.29</v>
-      </c>
       <c r="S29">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T29">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V29">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AC29">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AD29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AH29">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="AK29" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL29">
-        <v>1.04</v>
-      </c>
-      <c r="AM29">
-        <v>1.12</v>
-      </c>
-      <c r="AN29">
-        <v>4</v>
-      </c>
-      <c r="AO29">
-        <v>8</v>
-      </c>
-      <c r="AP29">
-        <v>1.14</v>
-      </c>
-      <c r="AQ29">
-        <v>1.23</v>
-      </c>
-      <c r="AR29">
-        <v>1.43</v>
-      </c>
-      <c r="AS29">
-        <v>1.75</v>
-      </c>
-      <c r="AT29">
-        <v>2.25</v>
-      </c>
-      <c r="AU29">
-        <v>4.8</v>
-      </c>
-      <c r="AV29">
-        <v>3.6</v>
-      </c>
-      <c r="AW29">
-        <v>2.5</v>
-      </c>
-      <c r="AX29">
-        <v>1.9</v>
-      </c>
-      <c r="AY29">
-        <v>1.53</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.2</v>
-      </c>
-      <c r="BC29">
-        <v>5</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>181</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45776.58333333334</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45776</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>1</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L30">
-        <v>2.72</v>
+        <v>1.36</v>
       </c>
       <c r="M30">
-        <v>3.54</v>
+        <v>5.2</v>
       </c>
       <c r="N30">
+        <v>7</v>
+      </c>
+      <c r="O30">
+        <v>1.2</v>
+      </c>
+      <c r="P30">
+        <v>15</v>
+      </c>
+      <c r="Q30">
+        <v>5</v>
+      </c>
+      <c r="R30">
+        <v>1.29</v>
+      </c>
+      <c r="S30">
+        <v>3.5</v>
+      </c>
+      <c r="T30">
+        <v>2.38</v>
+      </c>
+      <c r="U30">
+        <v>1.53</v>
+      </c>
+      <c r="V30">
+        <v>5.5</v>
+      </c>
+      <c r="W30">
+        <v>1.14</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>13</v>
+      </c>
+      <c r="Z30">
+        <v>1.15</v>
+      </c>
+      <c r="AA30">
+        <v>5.5</v>
+      </c>
+      <c r="AB30">
+        <v>1.5</v>
+      </c>
+      <c r="AC30">
         <v>2.3</v>
       </c>
-      <c r="O30">
-        <v>1.95</v>
-      </c>
-      <c r="P30">
-        <v>10</v>
-      </c>
-      <c r="Q30">
-        <v>1.95</v>
-      </c>
-      <c r="R30">
-        <v>1.31</v>
-      </c>
-      <c r="S30">
-        <v>3.2</v>
-      </c>
-      <c r="T30">
-        <v>2.53</v>
-      </c>
-      <c r="U30">
-        <v>1.47</v>
-      </c>
-      <c r="V30">
-        <v>5.8</v>
-      </c>
-      <c r="W30">
-        <v>1.06</v>
-      </c>
-      <c r="X30">
-        <v>1.04</v>
-      </c>
-      <c r="Y30">
-        <v>10</v>
-      </c>
-      <c r="Z30">
+      <c r="AD30">
+        <v>2.5</v>
+      </c>
+      <c r="AE30">
+        <v>1.53</v>
+      </c>
+      <c r="AF30">
+        <v>2.05</v>
+      </c>
+      <c r="AG30">
+        <v>1.7</v>
+      </c>
+      <c r="AH30">
+        <v>3.95</v>
+      </c>
+      <c r="AI30">
         <v>1.25</v>
       </c>
-      <c r="AA30">
-        <v>3.8</v>
-      </c>
-      <c r="AB30">
-        <v>1.77</v>
-      </c>
-      <c r="AC30">
-        <v>2</v>
-      </c>
-      <c r="AD30">
-        <v>2.9</v>
-      </c>
-      <c r="AE30">
-        <v>1.42</v>
-      </c>
-      <c r="AF30">
-        <v>1.6</v>
-      </c>
-      <c r="AG30">
-        <v>2.19</v>
-      </c>
-      <c r="AH30">
-        <v>4.4</v>
-      </c>
-      <c r="AI30">
-        <v>1.09</v>
-      </c>
       <c r="AJ30" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AK30" t="s">
-        <v>199</v>
-      </c>
-      <c r="AL30">
-        <v>1.25</v>
-      </c>
-      <c r="AM30">
-        <v>1.29</v>
-      </c>
-      <c r="AN30">
-        <v>1.44</v>
-      </c>
-      <c r="AO30">
-        <v>14</v>
-      </c>
-      <c r="AP30">
-        <v>1.18</v>
-      </c>
-      <c r="AQ30">
-        <v>1.3</v>
-      </c>
-      <c r="AR30">
-        <v>1.51</v>
-      </c>
-      <c r="AS30">
-        <v>1.87</v>
-      </c>
-      <c r="AT30">
-        <v>2.23</v>
-      </c>
-      <c r="AU30">
-        <v>4.3</v>
-      </c>
-      <c r="AV30">
-        <v>3.05</v>
-      </c>
-      <c r="AW30">
-        <v>2.32</v>
-      </c>
-      <c r="AX30">
-        <v>1.86</v>
-      </c>
-      <c r="AY30">
-        <v>1.56</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.95</v>
-      </c>
-      <c r="BC30">
-        <v>1.95</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45776.58333333334</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45776</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L31">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="M31">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q31">
         <v>2.5</v>
       </c>
       <c r="R31">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="T31">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB31">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AC31">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ31" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK31" t="s">
-        <v>200</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>7</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.62</v>
-      </c>
-      <c r="BC31">
-        <v>2.5</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45776.58333333334</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45776</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>1</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L32">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P32">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="R32">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="S32">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>2.53</v>
       </c>
       <c r="U32">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="V32">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AA32">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="AB32">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AC32">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AD32">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="AE32">
+        <v>1.42</v>
+      </c>
+      <c r="AF32">
+        <v>1.6</v>
+      </c>
+      <c r="AG32">
+        <v>2.19</v>
+      </c>
+      <c r="AH32">
+        <v>4.4</v>
+      </c>
+      <c r="AI32">
         <v>1.09</v>
       </c>
-      <c r="AF32">
-        <v>2.2</v>
-      </c>
-      <c r="AG32">
-        <v>1.57</v>
-      </c>
-      <c r="AH32">
-        <v>14.5</v>
-      </c>
-      <c r="AI32">
-        <v>1.02</v>
-      </c>
       <c r="AJ32" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="AK32" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL32">
-        <v>1.5</v>
-      </c>
-      <c r="AM32">
-        <v>1.47</v>
-      </c>
-      <c r="AN32">
-        <v>1.52</v>
-      </c>
-      <c r="AO32">
-        <v>6</v>
-      </c>
-      <c r="AP32">
-        <v>1.42</v>
-      </c>
-      <c r="AQ32">
-        <v>1.7</v>
-      </c>
-      <c r="AR32">
-        <v>2.1</v>
-      </c>
-      <c r="AS32">
-        <v>2.7</v>
-      </c>
-      <c r="AT32">
-        <v>3.6</v>
-      </c>
-      <c r="AU32">
-        <v>2.62</v>
-      </c>
-      <c r="AV32">
-        <v>2.05</v>
-      </c>
-      <c r="AW32">
-        <v>1.65</v>
-      </c>
-      <c r="AX32">
-        <v>1.4</v>
-      </c>
-      <c r="AY32">
-        <v>1.25</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>2.05</v>
-      </c>
-      <c r="BC32">
-        <v>2.5</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>182</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45776.58333333334</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45776</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E33" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -6470,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L33">
         <v>1.3</v>
@@ -6545,87 +4763,33 @@
         <v>1.17</v>
       </c>
       <c r="AJ33" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="AK33" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL33">
-        <v>1.05</v>
-      </c>
-      <c r="AM33">
-        <v>1.14</v>
-      </c>
-      <c r="AN33">
-        <v>3.6</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>1.23</v>
-      </c>
-      <c r="AQ33">
-        <v>1.43</v>
-      </c>
-      <c r="AR33">
-        <v>1.78</v>
-      </c>
-      <c r="AS33">
-        <v>2.3</v>
-      </c>
-      <c r="AT33">
-        <v>3.2</v>
-      </c>
-      <c r="AU33">
-        <v>3.6</v>
-      </c>
-      <c r="AV33">
-        <v>2.5</v>
-      </c>
-      <c r="AW33">
-        <v>1.87</v>
-      </c>
-      <c r="AX33">
-        <v>1.51</v>
-      </c>
-      <c r="AY33">
-        <v>1.29</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.2</v>
-      </c>
-      <c r="BC33">
-        <v>5</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>183</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45776.64583333334</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45776</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E34" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -6640,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L34">
         <v>2.39</v>
@@ -6715,87 +4879,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ34" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="AK34" t="s">
-        <v>169</v>
-      </c>
-      <c r="AL34">
-        <v>1.3</v>
-      </c>
-      <c r="AM34">
-        <v>1.3</v>
-      </c>
-      <c r="AN34">
-        <v>1.57</v>
-      </c>
-      <c r="AO34">
-        <v>12</v>
-      </c>
-      <c r="AP34">
-        <v>1.28</v>
-      </c>
-      <c r="AQ34">
-        <v>1.56</v>
-      </c>
-      <c r="AR34">
-        <v>1.95</v>
-      </c>
-      <c r="AS34">
-        <v>2.57</v>
-      </c>
-      <c r="AT34">
-        <v>3.5</v>
-      </c>
-      <c r="AU34">
-        <v>3.05</v>
-      </c>
-      <c r="AV34">
-        <v>2.21</v>
-      </c>
-      <c r="AW34">
-        <v>1.77</v>
-      </c>
-      <c r="AX34">
-        <v>1.42</v>
-      </c>
-      <c r="AY34">
-        <v>1.22</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>1.8</v>
-      </c>
-      <c r="BC34">
-        <v>2.25</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>150</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45776.65625</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45776</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F35" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -6810,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L35">
         <v>2.17</v>
@@ -6885,87 +4995,33 @@
         <v>1.12</v>
       </c>
       <c r="AJ35" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s">
-        <v>202</v>
-      </c>
-      <c r="AL35">
-        <v>1.31</v>
-      </c>
-      <c r="AM35">
-        <v>1.3</v>
-      </c>
-      <c r="AN35">
-        <v>1.68</v>
-      </c>
-      <c r="AO35">
-        <v>4</v>
-      </c>
-      <c r="AP35">
-        <v>1.22</v>
-      </c>
-      <c r="AQ35">
-        <v>1.42</v>
-      </c>
-      <c r="AR35">
-        <v>1.73</v>
-      </c>
-      <c r="AS35">
-        <v>2.25</v>
-      </c>
-      <c r="AT35">
-        <v>3.1</v>
-      </c>
-      <c r="AU35">
-        <v>3.9</v>
-      </c>
-      <c r="AV35">
-        <v>2.65</v>
-      </c>
-      <c r="AW35">
-        <v>1.95</v>
-      </c>
-      <c r="AX35">
-        <v>1.55</v>
-      </c>
-      <c r="AY35">
-        <v>1.31</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.67</v>
-      </c>
-      <c r="BC35">
-        <v>2.38</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>184</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45776.66666666666</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45776</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F36" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -6980,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L36">
         <v>2.1</v>
@@ -7055,87 +5111,33 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="AK36" t="s">
-        <v>203</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
-        <v>0</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>0</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>0</v>
-      </c>
-      <c r="AV36">
-        <v>0</v>
-      </c>
-      <c r="AW36">
-        <v>0</v>
-      </c>
-      <c r="AX36">
-        <v>0</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>1.73</v>
-      </c>
-      <c r="BC36">
-        <v>2.38</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>185</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45776.66666666666</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45776</v>
       </c>
       <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" t="s">
         <v>66</v>
       </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
-        <v>84</v>
-      </c>
       <c r="E37" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F37" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7150,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L37">
         <v>2.1</v>
@@ -7225,138 +5227,84 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="AK37" t="s">
-        <v>204</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
-      </c>
-      <c r="AO37">
-        <v>-1</v>
-      </c>
-      <c r="AP37">
-        <v>0</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37">
-        <v>0</v>
-      </c>
-      <c r="AV37">
-        <v>0</v>
-      </c>
-      <c r="AW37">
-        <v>0</v>
-      </c>
-      <c r="AX37">
-        <v>0</v>
-      </c>
-      <c r="AY37">
-        <v>0</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>1.67</v>
-      </c>
-      <c r="BC37">
-        <v>2.6</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>186</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45776.6875</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45776</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F38" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
         <v>1</v>
       </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
       <c r="K38" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L38">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="M38">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S38">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X38">
         <v>0</v>
@@ -7365,28 +5313,28 @@
         <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AA38">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB38">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF38">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG38">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH38">
         <v>0</v>
@@ -7395,138 +5343,84 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="AK38" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL38">
-        <v>0</v>
-      </c>
-      <c r="AM38">
-        <v>0</v>
-      </c>
-      <c r="AN38">
-        <v>0</v>
-      </c>
-      <c r="AO38">
-        <v>4</v>
-      </c>
-      <c r="AP38">
-        <v>0</v>
-      </c>
-      <c r="AQ38">
-        <v>0</v>
-      </c>
-      <c r="AR38">
-        <v>0</v>
-      </c>
-      <c r="AS38">
-        <v>0</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38">
-        <v>0</v>
-      </c>
-      <c r="AV38">
-        <v>0</v>
-      </c>
-      <c r="AW38">
-        <v>0</v>
-      </c>
-      <c r="AX38">
-        <v>0</v>
-      </c>
-      <c r="AY38">
-        <v>0</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.95</v>
-      </c>
-      <c r="BC38">
-        <v>2.3</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>187</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45776.79166666666</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45776</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F39" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>1</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="L39">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="N39">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="O39">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="P39">
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S39">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T39">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V39">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -7535,28 +5429,28 @@
         <v>0</v>
       </c>
       <c r="Z39">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AA39">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB39">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD39">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG39">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH39">
         <v>0</v>
@@ -7565,66 +5459,12 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="AK39" t="s">
-        <v>205</v>
-      </c>
-      <c r="AL39">
-        <v>0</v>
-      </c>
-      <c r="AM39">
-        <v>0</v>
-      </c>
-      <c r="AN39">
-        <v>0</v>
-      </c>
-      <c r="AO39">
-        <v>10</v>
-      </c>
-      <c r="AP39">
-        <v>0</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39">
-        <v>0</v>
-      </c>
-      <c r="AV39">
-        <v>0</v>
-      </c>
-      <c r="AW39">
-        <v>0</v>
-      </c>
-      <c r="AX39">
-        <v>0</v>
-      </c>
-      <c r="AY39">
-        <v>0</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.91</v>
-      </c>
-      <c r="BC39">
-        <v>2.4</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>144</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45776.79166666666</v>
       </c>
     </row>

--- a/jogos_2025-04-29.xlsx
+++ b/jogos_2025-04-29.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,19 +772,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="M3" t="n">
-        <v>3.51</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -871,10 +871,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45776.08333333334</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,49 +927,49 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.63</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>2.95</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45776.08333333334</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
         <v>3.6</v>
       </c>
       <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['49', '67', '77']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['33', '50']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45776.08333333334</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>2.86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['33', '50']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45776.08333333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.03</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
         <v>3.5</v>
@@ -1482,33 +1482,33 @@
         <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['49', '67', '77']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45776.08333333334</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -1564,78 +1564,78 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['32', '36']</t>
+          <t>['29', '55']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1648,7 +1648,7 @@
         <v>2.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45776.08333333334</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.77</v>
+        <v>3.66</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.25</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,31 +1740,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['76', '90+3']</t>
+          <t>['55', '59']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['38', '51']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.73</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,70 +1830,70 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="M11" t="n">
         <v>3.41</v>
       </c>
       <c r="N11" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.25</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['29', '55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.83</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,49 +1959,49 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="M12" t="n">
-        <v>3.66</v>
+        <v>3.32</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2010,19 +2010,19 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['55', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['32', '36']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45776.08333333334</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,49 +2088,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="M13" t="n">
-        <v>3.32</v>
+        <v>3.51</v>
       </c>
       <c r="N13" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2139,32 +2139,32 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45776.08333333334</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="M14" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.5</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['76', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['38', '51']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45776.08333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,70 +2604,70 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.76</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="O17" t="n">
         <v>3.4</v>
       </c>
       <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.96</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
         <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['53', '67']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['5', '12', '14', '19']</t>
+          <t>['49', '78']</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45776.125</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,76 +2707,76 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
@@ -2784,19 +2784,19 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['49', '78']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2806,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45776.125</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="N19" t="n">
-        <v>3.87</v>
+        <v>2.39</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
@@ -2895,50 +2895,50 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['53', '67']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['5', '12', '14', '19']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45776.125</v>
@@ -3342,119 +3342,119 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.36</v>
-      </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['12', '33', '40', '63']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45776.54166666666</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,55 +3507,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.4</v>
       </c>
-      <c r="O24" t="n">
-        <v>6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3565,14 +3565,14 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['25', '61', '76', '83']</t>
-        </is>
-      </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.75</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>4.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45776.54166666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,19 +3636,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
         <v>6</v>
@@ -3666,25 +3666,25 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['8', '41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45776.54166666666</v>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="N26" t="n">
-        <v>6.8</v>
+        <v>1.81</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '33', '40', '63']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>1.67</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45776.54166666666</v>
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3924,25 +3924,25 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['8', '41']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG27" t="n">
@@ -3967,10 +3967,10 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45776.54166666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4012,7 +4012,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
         <v>7</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45776.54166666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.36</v>
+        <v>6.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.91</v>
+        <v>6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['25', '61', '76', '83']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.36</v>
+        <v>3.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.75</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45776.54166666666</v>
@@ -4245,33 +4245,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>2.13</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['32', '46']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH30" t="n">
         <v>4</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AI30" t="n">
         <v>1.2</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45776.58333333334</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,80 +4410,80 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['2', '54']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AJ31" t="n">
         <v>2.5</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,91 +4513,91 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['32', '46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45776.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,19 +5029,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O36" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD36" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5118,17 +5118,17 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['31', '52']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ36" t="n">
         <v>2.38</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5247,17 +5247,17 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['31', '52']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ37" t="n">
         <v>2.38</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,70 +5442,70 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="N39" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="O39" t="n">
         <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T39" t="n">
         <v>4</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4.33</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X39" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['51', '53']</t>
+          <t>['43', '81']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
@@ -5515,10 +5515,10 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45776.79166666666</v>
@@ -5545,109 +5545,109 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="M40" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
         <v>3.5</v>
       </c>
       <c r="P40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['51', '53']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['43', '81']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ40" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45776.79166666666</v>
